--- a/AAII_Financials/Yearly/OSW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OSW_YR_FIN.xlsx
@@ -2888,10 +2888,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E59" s="3">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="F59" s="3">
         <v>900</v>
